--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_13-10-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_13-10-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Celotex_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3BBA184-7310-44CA-808D-9869CE740B1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E6FB3BB-2C09-4ADE-8673-F39B905A3F70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4080" yWindow="1740" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32790" yWindow="1665" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1120,9 +1120,6 @@
     <t>£14.03</t>
   </si>
   <si>
-    <t>£16.60</t>
-  </si>
-  <si>
     <t>£20.90</t>
   </si>
   <si>
@@ -1205,6 +1202,9 @@
   </si>
   <si>
     <t>£2756.16</t>
+  </si>
+  <si>
+    <t>£16.51</t>
   </si>
 </sst>
 </file>
@@ -1793,7 +1793,7 @@
         <v>273</v>
       </c>
       <c r="Q4" t="s">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="R4" t="s">
         <v>288</v>
@@ -1849,7 +1849,7 @@
         <v>79</v>
       </c>
       <c r="Q5" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="R5" t="s">
         <v>289</v>
@@ -1905,7 +1905,7 @@
         <v>274</v>
       </c>
       <c r="Q6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="R6" t="s">
         <v>290</v>
@@ -1961,7 +1961,7 @@
         <v>275</v>
       </c>
       <c r="Q7" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="R7" t="s">
         <v>291</v>
@@ -2017,7 +2017,7 @@
         <v>82</v>
       </c>
       <c r="Q8" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="R8" t="s">
         <v>292</v>
@@ -2073,7 +2073,7 @@
         <v>83</v>
       </c>
       <c r="Q9" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="R9" t="s">
         <v>293</v>
@@ -2129,7 +2129,7 @@
         <v>276</v>
       </c>
       <c r="Q10" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="R10" t="s">
         <v>294</v>
@@ -2185,7 +2185,7 @@
         <v>277</v>
       </c>
       <c r="Q11" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="R11" t="s">
         <v>295</v>
@@ -2241,7 +2241,7 @@
         <v>278</v>
       </c>
       <c r="Q12" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="R12" t="s">
         <v>296</v>
@@ -2297,7 +2297,7 @@
         <v>279</v>
       </c>
       <c r="Q13" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="R13" t="s">
         <v>297</v>
@@ -2353,7 +2353,7 @@
         <v>280</v>
       </c>
       <c r="Q14" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="R14" t="s">
         <v>298</v>
@@ -2409,7 +2409,7 @@
         <v>89</v>
       </c>
       <c r="Q15" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="R15" t="s">
         <v>299</v>
@@ -2465,7 +2465,7 @@
         <v>90</v>
       </c>
       <c r="Q16" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="R16" t="s">
         <v>105</v>
@@ -2521,7 +2521,7 @@
         <v>281</v>
       </c>
       <c r="Q17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="R17" t="s">
         <v>300</v>
@@ -2577,7 +2577,7 @@
         <v>92</v>
       </c>
       <c r="Q18" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="R18" t="s">
         <v>105</v>
@@ -2633,7 +2633,7 @@
         <v>282</v>
       </c>
       <c r="Q19" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="R19" t="s">
         <v>301</v>
@@ -2689,7 +2689,7 @@
         <v>94</v>
       </c>
       <c r="Q20" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="R20" t="s">
         <v>302</v>
@@ -2745,7 +2745,7 @@
         <v>95</v>
       </c>
       <c r="Q21" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="R21" t="s">
         <v>303</v>
@@ -2801,7 +2801,7 @@
         <v>283</v>
       </c>
       <c r="Q22" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="R22" t="s">
         <v>304</v>
@@ -2848,7 +2848,7 @@
         <v>227</v>
       </c>
       <c r="N23" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="O23" t="s">
         <v>269</v>
@@ -2857,7 +2857,7 @@
         <v>97</v>
       </c>
       <c r="Q23" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="R23" t="s">
         <v>305</v>
@@ -2913,7 +2913,7 @@
         <v>98</v>
       </c>
       <c r="Q24" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="R24" t="s">
         <v>306</v>
@@ -2969,7 +2969,7 @@
         <v>99</v>
       </c>
       <c r="Q25" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="R25" t="s">
         <v>307</v>
@@ -3081,7 +3081,7 @@
         <v>101</v>
       </c>
       <c r="Q27" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="R27" t="s">
         <v>308</v>
@@ -3128,7 +3128,7 @@
         <v>232</v>
       </c>
       <c r="N28" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="O28" t="s">
         <v>270</v>
@@ -3137,7 +3137,7 @@
         <v>284</v>
       </c>
       <c r="Q28" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="R28" t="s">
         <v>309</v>
@@ -3184,7 +3184,7 @@
         <v>233</v>
       </c>
       <c r="N29" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="O29" t="s">
         <v>271</v>
@@ -3193,7 +3193,7 @@
         <v>285</v>
       </c>
       <c r="Q29" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="R29" t="s">
         <v>310</v>
@@ -3240,7 +3240,7 @@
         <v>234</v>
       </c>
       <c r="N30" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="O30" t="s">
         <v>364</v>

--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_13-10-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_13-10-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Celotex_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB00734-401E-4041-9A94-4F7CAF342C35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D01F1C5-9472-4216-851A-D73886F9C463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32790" yWindow="1665" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30765" yWindow="1740" windowWidth="21600" windowHeight="10230" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -976,9 +976,6 @@
     <t>£2183.04</t>
   </si>
   <si>
-    <t>Error: 503 Server Error: Service Unavailable for url: https://www.tradeinsulations.co.uk/product/140mm-celotex-thermaclass/</t>
-  </si>
-  <si>
     <t>£1886.4</t>
   </si>
   <si>
@@ -1208,6 +1205,9 @@
   </si>
   <si>
     <t>£2207.68</t>
+  </si>
+  <si>
+    <t>£1972.64</t>
   </si>
 </sst>
 </file>
@@ -1646,7 +1646,7 @@
         <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G2" t="s">
         <v>23</v>
@@ -1714,7 +1714,7 @@
         <v>34</v>
       </c>
       <c r="J3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="K3" t="s">
         <v>35</v>
@@ -1735,7 +1735,7 @@
         <v>31</v>
       </c>
       <c r="Q3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="R3" t="s">
         <v>39</v>
@@ -1758,7 +1758,7 @@
         <v>42</v>
       </c>
       <c r="F4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G4" t="s">
         <v>43</v>
@@ -1770,7 +1770,7 @@
         <v>45</v>
       </c>
       <c r="J4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="K4" t="s">
         <v>46</v>
@@ -1791,7 +1791,7 @@
         <v>50</v>
       </c>
       <c r="Q4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="R4" t="s">
         <v>51</v>
@@ -1814,7 +1814,7 @@
         <v>54</v>
       </c>
       <c r="F5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G5" t="s">
         <v>55</v>
@@ -1826,7 +1826,7 @@
         <v>57</v>
       </c>
       <c r="J5" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="K5" t="s">
         <v>58</v>
@@ -1847,7 +1847,7 @@
         <v>54</v>
       </c>
       <c r="Q5" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="R5" t="s">
         <v>62</v>
@@ -1870,7 +1870,7 @@
         <v>65</v>
       </c>
       <c r="F6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G6" t="s">
         <v>66</v>
@@ -1882,7 +1882,7 @@
         <v>68</v>
       </c>
       <c r="J6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="K6" t="s">
         <v>69</v>
@@ -1903,7 +1903,7 @@
         <v>73</v>
       </c>
       <c r="Q6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="R6" t="s">
         <v>74</v>
@@ -1926,7 +1926,7 @@
         <v>77</v>
       </c>
       <c r="F7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G7" t="s">
         <v>78</v>
@@ -1938,7 +1938,7 @@
         <v>80</v>
       </c>
       <c r="J7" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="K7" t="s">
         <v>81</v>
@@ -1959,7 +1959,7 @@
         <v>85</v>
       </c>
       <c r="Q7" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="R7" t="s">
         <v>86</v>
@@ -1982,7 +1982,7 @@
         <v>89</v>
       </c>
       <c r="F8" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G8" t="s">
         <v>90</v>
@@ -1994,7 +1994,7 @@
         <v>92</v>
       </c>
       <c r="J8" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="K8" t="s">
         <v>93</v>
@@ -2015,7 +2015,7 @@
         <v>89</v>
       </c>
       <c r="Q8" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="R8" t="s">
         <v>97</v>
@@ -2038,7 +2038,7 @@
         <v>90</v>
       </c>
       <c r="F9" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G9" t="s">
         <v>100</v>
@@ -2050,7 +2050,7 @@
         <v>102</v>
       </c>
       <c r="J9" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K9" t="s">
         <v>103</v>
@@ -2071,7 +2071,7 @@
         <v>90</v>
       </c>
       <c r="Q9" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="R9" t="s">
         <v>107</v>
@@ -2094,7 +2094,7 @@
         <v>110</v>
       </c>
       <c r="F10" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G10" t="s">
         <v>111</v>
@@ -2106,7 +2106,7 @@
         <v>113</v>
       </c>
       <c r="J10" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="K10" t="s">
         <v>114</v>
@@ -2127,7 +2127,7 @@
         <v>118</v>
       </c>
       <c r="Q10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="R10" t="s">
         <v>119</v>
@@ -2150,7 +2150,7 @@
         <v>122</v>
       </c>
       <c r="F11" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G11" t="s">
         <v>123</v>
@@ -2162,7 +2162,7 @@
         <v>125</v>
       </c>
       <c r="J11" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="K11" t="s">
         <v>126</v>
@@ -2183,7 +2183,7 @@
         <v>130</v>
       </c>
       <c r="Q11" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="R11" t="s">
         <v>131</v>
@@ -2206,7 +2206,7 @@
         <v>134</v>
       </c>
       <c r="F12" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G12" t="s">
         <v>135</v>
@@ -2218,7 +2218,7 @@
         <v>137</v>
       </c>
       <c r="J12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="K12" t="s">
         <v>138</v>
@@ -2239,7 +2239,7 @@
         <v>142</v>
       </c>
       <c r="Q12" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="R12" t="s">
         <v>143</v>
@@ -2262,7 +2262,7 @@
         <v>146</v>
       </c>
       <c r="F13" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G13" t="s">
         <v>147</v>
@@ -2274,7 +2274,7 @@
         <v>148</v>
       </c>
       <c r="J13" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="K13" t="s">
         <v>149</v>
@@ -2295,7 +2295,7 @@
         <v>152</v>
       </c>
       <c r="Q13" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="R13" t="s">
         <v>153</v>
@@ -2318,7 +2318,7 @@
         <v>156</v>
       </c>
       <c r="F14" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G14" t="s">
         <v>157</v>
@@ -2330,7 +2330,7 @@
         <v>159</v>
       </c>
       <c r="J14" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="K14" t="s">
         <v>157</v>
@@ -2351,7 +2351,7 @@
         <v>163</v>
       </c>
       <c r="Q14" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="R14" t="s">
         <v>164</v>
@@ -2374,7 +2374,7 @@
         <v>167</v>
       </c>
       <c r="F15" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G15" t="s">
         <v>168</v>
@@ -2386,7 +2386,7 @@
         <v>170</v>
       </c>
       <c r="J15" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="K15" t="s">
         <v>171</v>
@@ -2407,7 +2407,7 @@
         <v>167</v>
       </c>
       <c r="Q15" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="R15" t="s">
         <v>175</v>
@@ -2442,7 +2442,7 @@
         <v>181</v>
       </c>
       <c r="J16" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="K16" t="s">
         <v>182</v>
@@ -2463,7 +2463,7 @@
         <v>178</v>
       </c>
       <c r="Q16" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="R16" t="s">
         <v>21</v>
@@ -2498,7 +2498,7 @@
         <v>191</v>
       </c>
       <c r="J17" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="K17" t="s">
         <v>192</v>
@@ -2519,7 +2519,7 @@
         <v>196</v>
       </c>
       <c r="Q17" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="R17" t="s">
         <v>197</v>
@@ -2542,7 +2542,7 @@
         <v>200</v>
       </c>
       <c r="F18" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G18" t="s">
         <v>21</v>
@@ -2575,7 +2575,7 @@
         <v>200</v>
       </c>
       <c r="Q18" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="R18" t="s">
         <v>21</v>
@@ -2610,7 +2610,7 @@
         <v>212</v>
       </c>
       <c r="J19" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="K19" t="s">
         <v>213</v>
@@ -2631,7 +2631,7 @@
         <v>217</v>
       </c>
       <c r="Q19" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="R19" t="s">
         <v>218</v>
@@ -2654,7 +2654,7 @@
         <v>221</v>
       </c>
       <c r="F20" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G20" t="s">
         <v>222</v>
@@ -2666,7 +2666,7 @@
         <v>224</v>
       </c>
       <c r="J20" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="K20" t="s">
         <v>225</v>
@@ -2687,7 +2687,7 @@
         <v>221</v>
       </c>
       <c r="Q20" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="R20" t="s">
         <v>229</v>
@@ -2710,7 +2710,7 @@
         <v>232</v>
       </c>
       <c r="F21" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G21" t="s">
         <v>233</v>
@@ -2722,7 +2722,7 @@
         <v>181</v>
       </c>
       <c r="J21" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="K21" t="s">
         <v>235</v>
@@ -2743,7 +2743,7 @@
         <v>232</v>
       </c>
       <c r="Q21" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="R21" t="s">
         <v>238</v>
@@ -2766,7 +2766,7 @@
         <v>241</v>
       </c>
       <c r="F22" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G22" t="s">
         <v>242</v>
@@ -2778,7 +2778,7 @@
         <v>244</v>
       </c>
       <c r="J22" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="K22" t="s">
         <v>245</v>
@@ -2799,7 +2799,7 @@
         <v>248</v>
       </c>
       <c r="Q22" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="R22" t="s">
         <v>249</v>
@@ -2822,7 +2822,7 @@
         <v>252</v>
       </c>
       <c r="F23" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G23" t="s">
         <v>253</v>
@@ -2834,7 +2834,7 @@
         <v>255</v>
       </c>
       <c r="J23" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="K23" t="s">
         <v>256</v>
@@ -2846,7 +2846,7 @@
         <v>257</v>
       </c>
       <c r="N23" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O23" t="s">
         <v>258</v>
@@ -2855,7 +2855,7 @@
         <v>252</v>
       </c>
       <c r="Q23" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="R23" t="s">
         <v>259</v>
@@ -2878,7 +2878,7 @@
         <v>262</v>
       </c>
       <c r="F24" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G24" t="s">
         <v>21</v>
@@ -2890,7 +2890,7 @@
         <v>264</v>
       </c>
       <c r="J24" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="K24" t="s">
         <v>265</v>
@@ -2911,7 +2911,7 @@
         <v>262</v>
       </c>
       <c r="Q24" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="R24" t="s">
         <v>268</v>
@@ -2934,7 +2934,7 @@
         <v>271</v>
       </c>
       <c r="F25" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G25" t="s">
         <v>21</v>
@@ -2946,7 +2946,7 @@
         <v>273</v>
       </c>
       <c r="J25" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="K25" t="s">
         <v>265</v>
@@ -2967,7 +2967,7 @@
         <v>271</v>
       </c>
       <c r="Q25" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="R25" t="s">
         <v>276</v>
@@ -3002,7 +3002,7 @@
         <v>21</v>
       </c>
       <c r="J26" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="K26" t="s">
         <v>21</v>
@@ -3046,7 +3046,7 @@
         <v>284</v>
       </c>
       <c r="F27" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G27" t="s">
         <v>21</v>
@@ -3058,7 +3058,7 @@
         <v>286</v>
       </c>
       <c r="J27" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="K27" t="s">
         <v>287</v>
@@ -3079,7 +3079,7 @@
         <v>284</v>
       </c>
       <c r="Q27" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="R27" t="s">
         <v>290</v>
@@ -3102,7 +3102,7 @@
         <v>293</v>
       </c>
       <c r="F28" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G28" t="s">
         <v>21</v>
@@ -3126,7 +3126,7 @@
         <v>297</v>
       </c>
       <c r="N28" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="O28" t="s">
         <v>298</v>
@@ -3135,7 +3135,7 @@
         <v>299</v>
       </c>
       <c r="Q28" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="R28" t="s">
         <v>300</v>
@@ -3158,7 +3158,7 @@
         <v>303</v>
       </c>
       <c r="F29" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G29" t="s">
         <v>21</v>
@@ -3182,7 +3182,7 @@
         <v>307</v>
       </c>
       <c r="N29" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="O29" t="s">
         <v>308</v>
@@ -3191,7 +3191,7 @@
         <v>309</v>
       </c>
       <c r="Q29" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="R29" t="s">
         <v>310</v>
@@ -3214,7 +3214,7 @@
         <v>313</v>
       </c>
       <c r="F30" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G30" t="s">
         <v>21</v>
@@ -3238,19 +3238,19 @@
         <v>317</v>
       </c>
       <c r="N30" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="O30" t="s">
+        <v>395</v>
+      </c>
+      <c r="P30" t="s">
         <v>318</v>
       </c>
-      <c r="P30" t="s">
+      <c r="Q30" t="s">
+        <v>21</v>
+      </c>
+      <c r="R30" t="s">
         <v>319</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>21</v>
-      </c>
-      <c r="R30" t="s">
-        <v>320</v>
       </c>
     </row>
   </sheetData>
